--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:19</t>
+    <t xml:space="preserve">2026-10-05 10:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
